--- a/Catch models/scenarios_sumarized_macarellus_cmsy.xlsx
+++ b/Catch models/scenarios_sumarized_macarellus_cmsy.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="85">
   <si>
     <t>stock</t>
   </si>
@@ -43,281 +43,293 @@
     <t>NN_CMSY_Euler-lotka methods</t>
   </si>
   <si>
-    <t>0.27 (0.10-0.59)
-0.14 (0.10-0.23)</t>
-  </si>
-  <si>
-    <t>41 (12-103)
-51 (31-77)</t>
-  </si>
-  <si>
-    <t>0.20 (0.07-0.33)
-0.24 (0.11-0.40)</t>
-  </si>
-  <si>
-    <t>RU r = 0.466
-RU bk = 0.013</t>
+    <t>0.42 (0.20-0.80)
+0.25 (0.17-0.36)</t>
+  </si>
+  <si>
+    <t>19 (7-43)
+21 (15-28)</t>
+  </si>
+  <si>
+    <t>0.12 (0.02-0.22)
+0.11 (0.03-0.22)</t>
+  </si>
+  <si>
+    <t>RU r = 0.413
+RU bk = -0.028</t>
   </si>
   <si>
     <t>NN_CMSY_Higher resilience</t>
   </si>
   <si>
-    <t>0.50 (0.30-0.79)
-0.38 (0.28-0.53)</t>
-  </si>
-  <si>
-    <t>19 (8-37)
-20 (15-26)</t>
-  </si>
-  <si>
-    <t>0.20 (0.07-0.33)
-0.21 (0.09-0.36)</t>
-  </si>
-  <si>
-    <t>RU r = 0.251
-RU bk = -0.052</t>
+    <t>0.65 (0.40-1.00)
+0.46 (0.34-0.65)</t>
+  </si>
+  <si>
+    <t>12 (5-23)
+13 (10-16)</t>
+  </si>
+  <si>
+    <t>0.12 (0.02-0.22)
+0.11 (0.03-0.24)</t>
+  </si>
+  <si>
+    <t>RU r = 0.259
+RU bk = -0.041</t>
   </si>
   <si>
     <t>NN_CMSY_lower resilience</t>
   </si>
   <si>
-    <t>0.16 (0.05-0.39)
+    <t>0.21 (0.05-0.60)
 0.08 (0.05-0.12)</t>
   </si>
   <si>
-    <t>74 (19-205)
-112 (64-168)</t>
-  </si>
-  <si>
-    <t>0.20 (0.07-0.33)
-0.25 (0.13-0.42)</t>
-  </si>
-  <si>
-    <t>RU r = 0.516
-RU bk = 0.071</t>
+    <t>51 (10-161)
+90 (48-134)</t>
+  </si>
+  <si>
+    <t>0.12 (0.02-0.22)
+0.14 (0.05-0.26)</t>
+  </si>
+  <si>
+    <t>RU r = 0.580
+RU bk = 0.104</t>
   </si>
   <si>
     <t>NN_CMSY_Non-informative_r</t>
   </si>
   <si>
+    <t>0.48 (0.10-1.50)
+0.14 (0.09-0.23)</t>
+  </si>
+  <si>
+    <t>23 (4-76)
+38 (23-58)</t>
+  </si>
+  <si>
+    <t>0.12 (0.02-0.22)
+0.12 (0.03-0.23)</t>
+  </si>
+  <si>
+    <t>RU r = 0.632
+RU bk = -0.047</t>
+  </si>
+  <si>
+    <t>Target_switch_Euler-lotka methods</t>
+  </si>
+  <si>
+    <t>0.42 (0.20-0.80)
+0.25 (0.18-0.37)</t>
+  </si>
+  <si>
+    <t>19 (7-42)
+21 (15-29)</t>
+  </si>
+  <si>
+    <t>0.45 (0.20-0.70)
+0.49 (0.27-0.70)</t>
+  </si>
+  <si>
+    <t>RU r = 0.413
+RU bk = 0.177</t>
+  </si>
+  <si>
+    <t>Target_switch_Higher resilience</t>
+  </si>
+  <si>
+    <t>0.65 (0.40-1.00)
+0.45 (0.34-0.61)</t>
+  </si>
+  <si>
+    <t>0.45 (0.20-0.70)
+0.55 (0.24-0.77)</t>
+  </si>
+  <si>
+    <t>RU r = 0.303
+RU bk = -0.040</t>
+  </si>
+  <si>
+    <t>Target_switch_lower resilience</t>
+  </si>
+  <si>
+    <t>51 (10-156)
+88 (52-131)</t>
+  </si>
+  <si>
+    <t>0.45 (0.20-0.70)
+0.41 (0.23-0.59)</t>
+  </si>
+  <si>
+    <t>RU r = 0.594
+RU bk = 0.288</t>
+  </si>
+  <si>
+    <t>Target_switch_Non-informative_r</t>
+  </si>
+  <si>
+    <t>0.48 (0.10-1.50)
+0.14 (0.09-0.24)</t>
+  </si>
+  <si>
+    <t>24 (4-77)
+39 (22-58)</t>
+  </si>
+  <si>
+    <t>0.45 (0.20-0.70)
+0.42 (0.22-0.60)</t>
+  </si>
+  <si>
+    <t>RU r = 0.604
+RU bk = 0.247</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_Euler-lotka methods</t>
+  </si>
+  <si>
+    <t>0.42 (0.20-0.80)
+0.26 (0.18-0.39)</t>
+  </si>
+  <si>
+    <t>19 (7-43)
+21 (15-29)</t>
+  </si>
+  <si>
+    <t>0.51 (0.01-1.00)
+0.54 (0.19-0.87)</t>
+  </si>
+  <si>
+    <t>RU r = 0.387
+RU bk = 0.428</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_Higher resilience</t>
+  </si>
+  <si>
+    <t>0.65 (0.40-1.00)
+0.49 (0.35-0.68)</t>
+  </si>
+  <si>
+    <t>12 (5-23)
+12 (9-16)</t>
+  </si>
+  <si>
+    <t>0.51 (0.01-1.00)
+0.66 (0.23-0.95)</t>
+  </si>
+  <si>
+    <t>RU r = 0.188
+RU bk = 0.141</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_lower resilience</t>
+  </si>
+  <si>
+    <t>0.22 (0.05-0.60)
+0.08 (0.05-0.12)</t>
+  </si>
+  <si>
+    <t>49 (10-156)
+86 (51-128)</t>
+  </si>
+  <si>
+    <t>0.51 (0.01-1.00)
+0.36 (0.10-0.66)</t>
+  </si>
+  <si>
+    <t>RU r = 0.594
+RU bk = 0.458</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_Non-informative_r</t>
+  </si>
+  <si>
     <t>0.49 (0.10-1.50)
-0.15 (0.10-0.24)</t>
-  </si>
-  <si>
-    <t>29 (5-96)
-47 (30-70)</t>
-  </si>
-  <si>
-    <t>0.20 (0.07-0.33)
-0.23 (0.11-0.37)</t>
-  </si>
-  <si>
-    <t>RU r = 0.625
-RU bk = 0.060</t>
-  </si>
-  <si>
-    <t>Target_switch_Euler-lotka methods</t>
-  </si>
-  <si>
-    <t>0.27 (0.10-0.59)
-0.15 (0.10-0.23)</t>
-  </si>
-  <si>
-    <t>40 (12-100)
-55 (35-79)</t>
-  </si>
-  <si>
-    <t>0.45 (0.20-0.70)
-0.48 (0.26-0.68)</t>
-  </si>
-  <si>
-    <t>RU r = 0.472
-RU bk = 0.189</t>
-  </si>
-  <si>
-    <t>Target_switch_Higher resilience</t>
-  </si>
-  <si>
-    <t>0.50 (0.30-0.79)
-0.40 (0.30-0.56)</t>
-  </si>
-  <si>
-    <t>19 (8-37)
-21 (15-27)</t>
-  </si>
-  <si>
-    <t>0.45 (0.20-0.70)
-0.48 (0.26-0.69)</t>
-  </si>
-  <si>
-    <t>RU r = 0.289
-RU bk = 0.135</t>
-  </si>
-  <si>
-    <t>Target_switch_lower resilience</t>
-  </si>
-  <si>
-    <t>0.16 (0.05-0.39)
-0.08 (0.05-0.13)</t>
-  </si>
-  <si>
-    <t>73 (19-201)
-113 (71-165)</t>
-  </si>
-  <si>
-    <t>0.45 (0.20-0.70)
-0.49 (0.28-0.69)</t>
-  </si>
-  <si>
-    <t>RU r = 0.513
-RU bk = 0.222</t>
-  </si>
-  <si>
-    <t>Target_switch_Non-informative_r</t>
+0.15 (0.10-0.25)</t>
+  </si>
+  <si>
+    <t>24 (4-80)
+41 (23-62)</t>
+  </si>
+  <si>
+    <t>0.50 (0.01-1.00)
+0.44 (0.09-0.75)</t>
+  </si>
+  <si>
+    <t>RU r = 0.631
+RU bk = 0.385</t>
+  </si>
+  <si>
+    <t>zBRT_Euler-lotka methods</t>
+  </si>
+  <si>
+    <t>0.42 (0.20-0.80)
+0.24 (0.17-0.35)</t>
+  </si>
+  <si>
+    <t>19 (7-43)
+22 (15-30)</t>
+  </si>
+  <si>
+    <t>0.20 (0.01-0.39)
+0.26 (0.04-0.55)</t>
+  </si>
+  <si>
+    <t>RU r = 0.411
+RU bk = -0.403</t>
+  </si>
+  <si>
+    <t>zBRT_Higher resilience</t>
+  </si>
+  <si>
+    <t>0.65 (0.40-1.00)
+0.46 (0.35-0.63)</t>
+  </si>
+  <si>
+    <t>0.20 (0.01-0.39)
+0.18 (0.03-0.44)</t>
+  </si>
+  <si>
+    <t>RU r = 0.303
+RU bk = -0.215</t>
+  </si>
+  <si>
+    <t>zBRT_lower resilience</t>
+  </si>
+  <si>
+    <t>0.21 (0.05-0.60)
+0.07 (0.05-0.12)</t>
+  </si>
+  <si>
+    <t>49 (10-154)
+86 (50-129)</t>
+  </si>
+  <si>
+    <t>0.20 (0.01-0.39)
+0.23 (0.06-0.42)</t>
+  </si>
+  <si>
+    <t>RU r = 0.574
+RU bk = 0.057</t>
+  </si>
+  <si>
+    <t>zBRT_Non-informative_r</t>
   </si>
   <si>
     <t>0.49 (0.10-1.50)
-0.16 (0.10-0.26)</t>
-  </si>
-  <si>
-    <t>28 (5-93)
-50 (31-73)</t>
-  </si>
-  <si>
-    <t>RU r = 0.610
-RU bk = 0.189</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_Euler-lotka methods</t>
-  </si>
-  <si>
-    <t>0.27 (0.10-0.59)
-0.15 (0.10-0.24)</t>
-  </si>
-  <si>
-    <t>41 (12-103)
-56 (35-82)</t>
-  </si>
-  <si>
-    <t>0.51 (0.01-1.00)
-0.52 (0.16-0.82)</t>
-  </si>
-  <si>
-    <t>RU r = 0.455
-RU bk = 0.471</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_Higher resilience</t>
-  </si>
-  <si>
-    <t>0.50 (0.30-0.79)
-0.42 (0.30-0.59)</t>
-  </si>
-  <si>
-    <t>19 (8-37)
-21 (15-28)</t>
-  </si>
-  <si>
-    <t>0.50 (0.01-1.00)
-0.54 (0.20-0.86)</t>
-  </si>
-  <si>
-    <t>RU r = 0.232
-RU bk = 0.404</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_lower resilience</t>
-  </si>
-  <si>
-    <t>74 (19-201)
-115 (71-168)</t>
-  </si>
-  <si>
-    <t>0.50 (0.01-1.00)
-0.54 (0.27-0.85)</t>
-  </si>
-  <si>
-    <t>RU r = 0.489
-RU bk = 0.504</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_Non-informative_r</t>
-  </si>
-  <si>
-    <t>0.49 (0.10-1.50)
-0.17 (0.10-0.28)</t>
-  </si>
-  <si>
-    <t>29 (5-95)
-51 (32-75)</t>
-  </si>
-  <si>
-    <t>RU r = 0.576
-RU bk = 0.450</t>
-  </si>
-  <si>
-    <t>zBRT_Euler-lotka methods</t>
-  </si>
-  <si>
-    <t>40 (12-100)
-54 (35-79)</t>
-  </si>
-  <si>
-    <t>0.37 (0.05-0.69)
-0.45 (0.23-0.71)</t>
-  </si>
-  <si>
-    <t>RU r = 0.468
-RU bk = 0.335</t>
-  </si>
-  <si>
-    <t>zBRT_Higher resilience</t>
-  </si>
-  <si>
-    <t>0.50 (0.30-0.79)
-0.40 (0.29-0.56)</t>
-  </si>
-  <si>
-    <t>19 (8-38)
-21 (15-28)</t>
-  </si>
-  <si>
-    <t>0.37 (0.05-0.69)
-0.46 (0.19-0.73)</t>
-  </si>
-  <si>
-    <t>RU r = 0.236
-RU bk = 0.229</t>
-  </si>
-  <si>
-    <t>zBRT_lower resilience</t>
-  </si>
-  <si>
-    <t>73 (18-204)
-114 (69-170)</t>
-  </si>
-  <si>
-    <t>0.37 (0.05-0.69)
-0.49 (0.24-0.72)</t>
-  </si>
-  <si>
-    <t>RU r = 0.518
-RU bk = 0.327</t>
-  </si>
-  <si>
-    <t>zBRT_Non-informative_r</t>
-  </si>
-  <si>
-    <t>29 (5-96)
-50 (31-72)</t>
-  </si>
-  <si>
-    <t>0.37 (0.05-0.69)
-0.41 (0.19-0.67)</t>
-  </si>
-  <si>
-    <t>RU r = 0.617
-RU bk = 0.338</t>
+0.14 (0.09-0.21)</t>
+  </si>
+  <si>
+    <t>24 (4-80)
+42 (25-63)</t>
+  </si>
+  <si>
+    <t>0.20 (0.01-0.39)
+0.23 (0.06-0.45)</t>
+  </si>
+  <si>
+    <t>RU r = 0.645
+RU bk = -0.044</t>
   </si>
 </sst>
 </file>
@@ -706,7 +718,7 @@
         <v>12</v>
       </c>
       <c r="G2">
-        <v>8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -729,7 +741,7 @@
         <v>17</v>
       </c>
       <c r="G3">
-        <v>4.8</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -752,7 +764,7 @@
         <v>22</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -775,7 +787,7 @@
         <v>27</v>
       </c>
       <c r="G5">
-        <v>4.399999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -798,7 +810,7 @@
         <v>32</v>
       </c>
       <c r="G6">
-        <v>38.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -812,16 +824,16 @@
         <v>34</v>
       </c>
       <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
         <v>35</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>36</v>
       </c>
-      <c r="F7" t="s">
-        <v>37</v>
-      </c>
       <c r="G7">
-        <v>29.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -829,22 +841,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
         <v>38</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>39</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>40</v>
       </c>
-      <c r="E8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" t="s">
-        <v>42</v>
-      </c>
       <c r="G8">
-        <v>42.7</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -852,22 +864,22 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
         <v>43</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>44</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>45</v>
       </c>
-      <c r="E9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" t="s">
-        <v>46</v>
-      </c>
       <c r="G9">
-        <v>24.2</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -875,22 +887,22 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>48</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>49</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>50</v>
       </c>
-      <c r="F10" t="s">
-        <v>51</v>
-      </c>
       <c r="G10">
-        <v>79.5</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -898,22 +910,22 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" t="s">
         <v>52</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>53</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>54</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>55</v>
       </c>
-      <c r="F11" t="s">
-        <v>56</v>
-      </c>
       <c r="G11">
-        <v>75.8</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -921,10 +933,10 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" t="s">
         <v>57</v>
-      </c>
-      <c r="C12" t="s">
-        <v>39</v>
       </c>
       <c r="D12" t="s">
         <v>58</v>
@@ -936,7 +948,7 @@
         <v>60</v>
       </c>
       <c r="G12">
-        <v>78.60000000000001</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -953,13 +965,13 @@
         <v>63</v>
       </c>
       <c r="E13" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G13">
-        <v>73.3</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -967,22 +979,22 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G14">
-        <v>40.7</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -990,22 +1002,22 @@
         <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G15">
-        <v>29.8</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1013,22 +1025,22 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G16">
-        <v>45</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1036,22 +1048,22 @@
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E17" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G17">
-        <v>25.6</v>
+        <v>18.4</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/scenarios_sumarized_macarellus_cmsy.xlsx
+++ b/Catch models/scenarios_sumarized_macarellus_cmsy.xlsx
@@ -43,39 +43,39 @@
     <t>NN_CMSY_Euler-lotka methods</t>
   </si>
   <si>
-    <t>0.42 (0.20-0.80)
-0.25 (0.17-0.36)</t>
-  </si>
-  <si>
-    <t>19 (7-43)
-21 (15-28)</t>
-  </si>
-  <si>
-    <t>0.12 (0.02-0.22)
-0.11 (0.03-0.22)</t>
-  </si>
-  <si>
-    <t>RU r = 0.413
-RU bk = -0.028</t>
+    <t>0.43 (0.20-0.80)
+0.24 (0.17-0.36)</t>
+  </si>
+  <si>
+    <t>23 (9-53)
+29 (20-37)</t>
+  </si>
+  <si>
+    <t>0.14 (0.03-0.25)
+0.15 (0.04-0.29)</t>
+  </si>
+  <si>
+    <t>RU r = 0.392
+RU bk = -0.089</t>
   </si>
   <si>
     <t>NN_CMSY_Higher resilience</t>
   </si>
   <si>
     <t>0.65 (0.40-1.00)
-0.46 (0.34-0.65)</t>
-  </si>
-  <si>
-    <t>12 (5-23)
-13 (10-16)</t>
-  </si>
-  <si>
-    <t>0.12 (0.02-0.22)
-0.11 (0.03-0.24)</t>
-  </si>
-  <si>
-    <t>RU r = 0.259
-RU bk = -0.041</t>
+0.47 (0.36-0.66)</t>
+  </si>
+  <si>
+    <t>14 (6-29)
+17 (13-21)</t>
+  </si>
+  <si>
+    <t>0.14 (0.03-0.25)
+0.13 (0.04-0.26)</t>
+  </si>
+  <si>
+    <t>RU r = 0.260
+RU bk = -0.104</t>
   </si>
   <si>
     <t>NN_CMSY_lower resilience</t>
@@ -85,251 +85,251 @@
 0.08 (0.05-0.12)</t>
   </si>
   <si>
-    <t>51 (10-161)
-90 (48-134)</t>
-  </si>
-  <si>
-    <t>0.12 (0.02-0.22)
-0.14 (0.05-0.26)</t>
-  </si>
-  <si>
-    <t>RU r = 0.580
-RU bk = 0.104</t>
+    <t>63 (12-198)
+107 (59-161)</t>
+  </si>
+  <si>
+    <t>0.14 (0.03-0.25)
+0.18 (0.08-0.31)</t>
+  </si>
+  <si>
+    <t>RU r = 0.586
+RU bk = 0.131</t>
   </si>
   <si>
     <t>NN_CMSY_Non-informative_r</t>
   </si>
   <si>
     <t>0.48 (0.10-1.50)
-0.14 (0.09-0.23)</t>
-  </si>
-  <si>
-    <t>23 (4-76)
-38 (23-58)</t>
-  </si>
-  <si>
-    <t>0.12 (0.02-0.22)
-0.12 (0.03-0.23)</t>
-  </si>
-  <si>
-    <t>RU r = 0.632
-RU bk = -0.047</t>
+0.14 (0.09-0.22)</t>
+  </si>
+  <si>
+    <t>29 (5-95)
+46 (30-68)</t>
+  </si>
+  <si>
+    <t>0.14 (0.03-0.25)
+0.16 (0.07-0.27)</t>
+  </si>
+  <si>
+    <t>RU r = 0.616
+RU bk = 0.182</t>
   </si>
   <si>
     <t>Target_switch_Euler-lotka methods</t>
-  </si>
-  <si>
-    <t>0.42 (0.20-0.80)
-0.25 (0.18-0.37)</t>
-  </si>
-  <si>
-    <t>19 (7-42)
-21 (15-29)</t>
-  </si>
-  <si>
-    <t>0.45 (0.20-0.70)
-0.49 (0.27-0.70)</t>
-  </si>
-  <si>
-    <t>RU r = 0.413
-RU bk = 0.177</t>
-  </si>
-  <si>
-    <t>Target_switch_Higher resilience</t>
-  </si>
-  <si>
-    <t>0.65 (0.40-1.00)
-0.45 (0.34-0.61)</t>
-  </si>
-  <si>
-    <t>0.45 (0.20-0.70)
-0.55 (0.24-0.77)</t>
-  </si>
-  <si>
-    <t>RU r = 0.303
-RU bk = -0.040</t>
-  </si>
-  <si>
-    <t>Target_switch_lower resilience</t>
-  </si>
-  <si>
-    <t>51 (10-156)
-88 (52-131)</t>
-  </si>
-  <si>
-    <t>0.45 (0.20-0.70)
-0.41 (0.23-0.59)</t>
-  </si>
-  <si>
-    <t>RU r = 0.594
-RU bk = 0.288</t>
-  </si>
-  <si>
-    <t>Target_switch_Non-informative_r</t>
-  </si>
-  <si>
-    <t>0.48 (0.10-1.50)
-0.14 (0.09-0.24)</t>
-  </si>
-  <si>
-    <t>24 (4-77)
-39 (22-58)</t>
-  </si>
-  <si>
-    <t>0.45 (0.20-0.70)
-0.42 (0.22-0.60)</t>
-  </si>
-  <si>
-    <t>RU r = 0.604
-RU bk = 0.247</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_Euler-lotka methods</t>
-  </si>
-  <si>
-    <t>0.42 (0.20-0.80)
-0.26 (0.18-0.39)</t>
-  </si>
-  <si>
-    <t>19 (7-43)
-21 (15-29)</t>
-  </si>
-  <si>
-    <t>0.51 (0.01-1.00)
-0.54 (0.19-0.87)</t>
-  </si>
-  <si>
-    <t>RU r = 0.387
-RU bk = 0.428</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_Higher resilience</t>
-  </si>
-  <si>
-    <t>0.65 (0.40-1.00)
-0.49 (0.35-0.68)</t>
-  </si>
-  <si>
-    <t>12 (5-23)
-12 (9-16)</t>
-  </si>
-  <si>
-    <t>0.51 (0.01-1.00)
-0.66 (0.23-0.95)</t>
-  </si>
-  <si>
-    <t>RU r = 0.188
-RU bk = 0.141</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_lower resilience</t>
-  </si>
-  <si>
-    <t>0.22 (0.05-0.60)
-0.08 (0.05-0.12)</t>
-  </si>
-  <si>
-    <t>49 (10-156)
-86 (51-128)</t>
-  </si>
-  <si>
-    <t>0.51 (0.01-1.00)
-0.36 (0.10-0.66)</t>
-  </si>
-  <si>
-    <t>RU r = 0.594
-RU bk = 0.458</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_Non-informative_r</t>
-  </si>
-  <si>
-    <t>0.49 (0.10-1.50)
-0.15 (0.10-0.25)</t>
-  </si>
-  <si>
-    <t>24 (4-80)
-41 (23-62)</t>
-  </si>
-  <si>
-    <t>0.50 (0.01-1.00)
-0.44 (0.09-0.75)</t>
-  </si>
-  <si>
-    <t>RU r = 0.631
-RU bk = 0.385</t>
-  </si>
-  <si>
-    <t>zBRT_Euler-lotka methods</t>
   </si>
   <si>
     <t>0.42 (0.20-0.80)
 0.24 (0.17-0.35)</t>
   </si>
   <si>
-    <t>19 (7-43)
-22 (15-30)</t>
-  </si>
-  <si>
-    <t>0.20 (0.01-0.39)
-0.26 (0.04-0.55)</t>
-  </si>
-  <si>
-    <t>RU r = 0.411
-RU bk = -0.403</t>
-  </si>
-  <si>
-    <t>zBRT_Higher resilience</t>
+    <t>23 (9-52)
+29 (20-38)</t>
+  </si>
+  <si>
+    <t>0.25 (0.01-0.50)
+0.27 (0.06-0.60)</t>
+  </si>
+  <si>
+    <t>RU r = 0.413
+RU bk = -0.117</t>
+  </si>
+  <si>
+    <t>Target_switch_Higher resilience</t>
   </si>
   <si>
     <t>0.65 (0.40-1.00)
 0.46 (0.35-0.63)</t>
   </si>
   <si>
-    <t>0.20 (0.01-0.39)
-0.18 (0.03-0.44)</t>
-  </si>
-  <si>
-    <t>RU r = 0.303
-RU bk = -0.215</t>
-  </si>
-  <si>
-    <t>zBRT_lower resilience</t>
+    <t>14 (6-29)
+17 (13-22)</t>
+  </si>
+  <si>
+    <t>0.25 (0.01-0.50)
+0.29 (0.07-0.55)</t>
+  </si>
+  <si>
+    <t>RU r = 0.291
+RU bk = 0.004</t>
+  </si>
+  <si>
+    <t>Target_switch_lower resilience</t>
   </si>
   <si>
     <t>0.21 (0.05-0.60)
 0.07 (0.05-0.12)</t>
   </si>
   <si>
-    <t>49 (10-154)
-86 (50-129)</t>
-  </si>
-  <si>
-    <t>0.20 (0.01-0.39)
-0.23 (0.06-0.42)</t>
-  </si>
-  <si>
-    <t>RU r = 0.574
-RU bk = 0.057</t>
+    <t>62 (12-192)
+104 (60-156)</t>
+  </si>
+  <si>
+    <t>0.26 (0.01-0.50)
+0.29 (0.11-0.50)</t>
+  </si>
+  <si>
+    <t>RU r = 0.585
+RU bk = 0.297</t>
+  </si>
+  <si>
+    <t>Target_switch_Non-informative_r</t>
+  </si>
+  <si>
+    <t>0.49 (0.10-1.50)
+0.14 (0.09-0.23)</t>
+  </si>
+  <si>
+    <t>29 (5-98)
+49 (31-74)</t>
+  </si>
+  <si>
+    <t>0.25 (0.01-0.50)
+0.31 (0.13-0.52)</t>
+  </si>
+  <si>
+    <t>RU r = 0.630
+RU bk = 0.317</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_Euler-lotka methods</t>
+  </si>
+  <si>
+    <t>0.43 (0.20-0.80)
+0.25 (0.17-0.37)</t>
+  </si>
+  <si>
+    <t>24 (9-53)
+28 (20-38)</t>
+  </si>
+  <si>
+    <t>0.50 (0.01-1.00)
+0.38 (0.06-0.68)</t>
+  </si>
+  <si>
+    <t>RU r = 0.389
+RU bk = 0.338</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_Higher resilience</t>
+  </si>
+  <si>
+    <t>0.65 (0.40-1.00)
+0.49 (0.36-0.68)</t>
+  </si>
+  <si>
+    <t>15 (6-28)
+16 (12-21)</t>
+  </si>
+  <si>
+    <t>0.50 (0.01-1.00)
+0.67 (0.24-0.93)</t>
+  </si>
+  <si>
+    <t>RU r = 0.232
+RU bk = 0.292</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_lower resilience</t>
+  </si>
+  <si>
+    <t>62 (12-191)
+102 (61-153)</t>
+  </si>
+  <si>
+    <t>0.50 (0.01-1.00)
+0.36 (0.14-0.61)</t>
+  </si>
+  <si>
+    <t>RU r = 0.590
+RU bk = 0.609</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_Non-informative_r</t>
+  </si>
+  <si>
+    <t>29 (5-95)
+47 (30-69)</t>
+  </si>
+  <si>
+    <t>0.50 (0.01-1.00)
+0.37 (0.08-0.61)</t>
+  </si>
+  <si>
+    <t>RU r = 0.619
+RU bk = 0.422</t>
+  </si>
+  <si>
+    <t>zBRT_Euler-lotka methods</t>
+  </si>
+  <si>
+    <t>0.43 (0.20-0.80)
+0.24 (0.17-0.37)</t>
+  </si>
+  <si>
+    <t>24 (9-54)
+29 (20-38)</t>
+  </si>
+  <si>
+    <t>0.23 (0.01-0.45)
+0.25 (0.05-0.51)</t>
+  </si>
+  <si>
+    <t>RU r = 0.368
+RU bk = -0.117</t>
+  </si>
+  <si>
+    <t>zBRT_Higher resilience</t>
+  </si>
+  <si>
+    <t>0.65 (0.40-1.00)
+0.47 (0.35-0.63)</t>
+  </si>
+  <si>
+    <t>15 (6-29)
+17 (13-22)</t>
+  </si>
+  <si>
+    <t>0.23 (0.01-0.45)
+0.24 (0.06-0.52)</t>
+  </si>
+  <si>
+    <t>RU r = 0.239
+RU bk = -0.095</t>
+  </si>
+  <si>
+    <t>zBRT_lower resilience</t>
+  </si>
+  <si>
+    <t>61 (13-189)
+99 (58-150)</t>
+  </si>
+  <si>
+    <t>0.23 (0.01-0.45)
+0.29 (0.12-0.48)</t>
+  </si>
+  <si>
+    <t>RU r = 0.572
+RU bk = 0.329</t>
   </si>
   <si>
     <t>zBRT_Non-informative_r</t>
   </si>
   <si>
-    <t>0.49 (0.10-1.50)
-0.14 (0.09-0.21)</t>
-  </si>
-  <si>
-    <t>24 (4-80)
-42 (25-63)</t>
-  </si>
-  <si>
-    <t>0.20 (0.01-0.39)
-0.23 (0.06-0.45)</t>
-  </si>
-  <si>
-    <t>RU r = 0.645
-RU bk = -0.044</t>
+    <t>0.48 (0.10-1.50)
+0.15 (0.10-0.24)</t>
+  </si>
+  <si>
+    <t>29 (5-98)
+49 (31-72)</t>
+  </si>
+  <si>
+    <t>0.23 (0.01-0.45)
+0.27 (0.08-0.50)</t>
+  </si>
+  <si>
+    <t>RU r = 0.659
+RU bk = 0.098</t>
   </si>
 </sst>
 </file>
@@ -718,7 +718,7 @@
         <v>12</v>
       </c>
       <c r="G2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -741,7 +741,7 @@
         <v>17</v>
       </c>
       <c r="G3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -764,7 +764,7 @@
         <v>22</v>
       </c>
       <c r="G4">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -787,7 +787,7 @@
         <v>27</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0.8999999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -810,7 +810,7 @@
         <v>32</v>
       </c>
       <c r="G6">
-        <v>11</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -824,16 +824,16 @@
         <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -841,22 +841,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G8">
-        <v>26.2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -864,22 +864,22 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G9">
-        <v>12.4</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -887,22 +887,22 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G10">
-        <v>64.2</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -910,22 +910,22 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G11">
-        <v>58.2</v>
+        <v>56.59999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -933,22 +933,22 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G12">
-        <v>68</v>
+        <v>67.10000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -956,10 +956,10 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
         <v>63</v>
@@ -971,7 +971,7 @@
         <v>65</v>
       </c>
       <c r="G13">
-        <v>61.9</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -994,7 +994,7 @@
         <v>70</v>
       </c>
       <c r="G14">
-        <v>14.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1008,16 +1008,16 @@
         <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G15">
-        <v>18.2</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1025,10 +1025,10 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s">
         <v>77</v>
@@ -1040,7 +1040,7 @@
         <v>79</v>
       </c>
       <c r="G16">
-        <v>14.8</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1063,7 +1063,7 @@
         <v>84</v>
       </c>
       <c r="G17">
-        <v>18.4</v>
+        <v>21.6</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/scenarios_sumarized_macarellus_cmsy.xlsx
+++ b/Catch models/scenarios_sumarized_macarellus_cmsy.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="84">
   <si>
     <t>stock</t>
   </si>
@@ -43,293 +43,289 @@
     <t>NN_CMSY_Euler-lotka methods</t>
   </si>
   <si>
-    <t>0.43 (0.20-0.80)
-0.24 (0.17-0.36)</t>
-  </si>
-  <si>
-    <t>23 (9-53)
-29 (20-37)</t>
+    <t>0.42 (0.20-0.80)
+0.24 (0.16-0.36)</t>
+  </si>
+  <si>
+    <t>23 (9-52)
+30 (21-40)</t>
   </si>
   <si>
     <t>0.14 (0.03-0.25)
-0.15 (0.04-0.29)</t>
-  </si>
-  <si>
-    <t>RU r = 0.392
-RU bk = -0.089</t>
+0.14 (0.05-0.26)</t>
+  </si>
+  <si>
+    <t>RU r = 0.359
+RU bk = 0.020</t>
   </si>
   <si>
     <t>NN_CMSY_Higher resilience</t>
   </si>
   <si>
     <t>0.65 (0.40-1.00)
-0.47 (0.36-0.66)</t>
+0.47 (0.35-0.62)</t>
+  </si>
+  <si>
+    <t>14 (6-28)
+17 (13-22)</t>
+  </si>
+  <si>
+    <t>0.14 (0.03-0.25)
+0.13 (0.05-0.25)</t>
+  </si>
+  <si>
+    <t>RU r = 0.291
+RU bk = -0.024</t>
+  </si>
+  <si>
+    <t>NN_CMSY_lower resilience</t>
+  </si>
+  <si>
+    <t>0.21 (0.05-0.60)
+0.07 (0.04-0.11)</t>
+  </si>
+  <si>
+    <t>61 (12-197)
+112 (65-169)</t>
+  </si>
+  <si>
+    <t>0.14 (0.03-0.25)
+0.17 (0.07-0.30)</t>
+  </si>
+  <si>
+    <t>RU r = 0.590
+RU bk = 0.110</t>
+  </si>
+  <si>
+    <t>NN_CMSY_Non-informative_r</t>
+  </si>
+  <si>
+    <t>0.49 (0.10-1.50)
+0.13 (0.08-0.20)</t>
+  </si>
+  <si>
+    <t>29 (5-96)
+53 (35-78)</t>
+  </si>
+  <si>
+    <t>0.14 (0.03-0.25)
+0.14 (0.05-0.25)</t>
+  </si>
+  <si>
+    <t>RU r = 0.632
+RU bk = 0.119</t>
+  </si>
+  <si>
+    <t>Target_switch_Euler-lotka methods</t>
+  </si>
+  <si>
+    <t>24 (9-53)
+31 (21-41)</t>
+  </si>
+  <si>
+    <t>0.26 (0.01-0.50)
+0.26 (0.05-0.55)</t>
+  </si>
+  <si>
+    <t>RU r = 0.393
+RU bk = -0.096</t>
+  </si>
+  <si>
+    <t>Target_switch_Higher resilience</t>
+  </si>
+  <si>
+    <t>0.65 (0.40-1.00)
+0.46 (0.34-0.64)</t>
   </si>
   <si>
     <t>14 (6-29)
-17 (13-21)</t>
-  </si>
-  <si>
-    <t>0.14 (0.03-0.25)
-0.13 (0.04-0.26)</t>
-  </si>
-  <si>
-    <t>RU r = 0.260
-RU bk = -0.104</t>
-  </si>
-  <si>
-    <t>NN_CMSY_lower resilience</t>
-  </si>
-  <si>
-    <t>0.21 (0.05-0.60)
-0.08 (0.05-0.12)</t>
-  </si>
-  <si>
-    <t>63 (12-198)
-107 (59-161)</t>
-  </si>
-  <si>
-    <t>0.14 (0.03-0.25)
-0.18 (0.08-0.31)</t>
-  </si>
-  <si>
-    <t>RU r = 0.586
-RU bk = 0.131</t>
-  </si>
-  <si>
-    <t>NN_CMSY_Non-informative_r</t>
-  </si>
-  <si>
-    <t>0.48 (0.10-1.50)
-0.14 (0.09-0.22)</t>
-  </si>
-  <si>
-    <t>29 (5-95)
-46 (30-68)</t>
-  </si>
-  <si>
-    <t>0.14 (0.03-0.25)
-0.16 (0.07-0.27)</t>
-  </si>
-  <si>
-    <t>RU r = 0.616
-RU bk = 0.182</t>
-  </si>
-  <si>
-    <t>Target_switch_Euler-lotka methods</t>
+17 (12-22)</t>
+  </si>
+  <si>
+    <t>0.25 (0.01-0.50)
+0.29 (0.05-0.63)</t>
+  </si>
+  <si>
+    <t>RU r = 0.216
+RU bk = -0.125</t>
+  </si>
+  <si>
+    <t>Target_switch_lower resilience</t>
+  </si>
+  <si>
+    <t>61 (12-192)
+110 (65-169)</t>
+  </si>
+  <si>
+    <t>0.25 (0.01-0.50)
+0.30 (0.10-0.47)</t>
+  </si>
+  <si>
+    <t>RU r = 0.593
+RU bk = 0.305</t>
+  </si>
+  <si>
+    <t>Target_switch_Non-informative_r</t>
+  </si>
+  <si>
+    <t>0.49 (0.10-1.50)
+0.14 (0.09-0.21)</t>
+  </si>
+  <si>
+    <t>29 (5-99)
+55 (35-81)</t>
+  </si>
+  <si>
+    <t>0.26 (0.01-0.50)
+0.30 (0.08-0.51)</t>
+  </si>
+  <si>
+    <t>RU r = 0.647
+RU bk = 0.107</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_Euler-lotka methods</t>
   </si>
   <si>
     <t>0.42 (0.20-0.80)
-0.24 (0.17-0.35)</t>
-  </si>
-  <si>
-    <t>23 (9-52)
-29 (20-38)</t>
-  </si>
-  <si>
-    <t>0.25 (0.01-0.50)
-0.27 (0.06-0.60)</t>
-  </si>
-  <si>
-    <t>RU r = 0.413
-RU bk = -0.117</t>
-  </si>
-  <si>
-    <t>Target_switch_Higher resilience</t>
+0.25 (0.17-0.37)</t>
+  </si>
+  <si>
+    <t>24 (8-54)
+30 (21-41)</t>
+  </si>
+  <si>
+    <t>0.51 (0.01-1.00)
+0.41 (0.06-0.82)</t>
+  </si>
+  <si>
+    <t>RU r = 0.404
+RU bk = 0.297</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_Higher resilience</t>
   </si>
   <si>
     <t>0.65 (0.40-1.00)
-0.46 (0.35-0.63)</t>
-  </si>
-  <si>
-    <t>14 (6-29)
-17 (13-22)</t>
-  </si>
-  <si>
-    <t>0.25 (0.01-0.50)
-0.29 (0.07-0.55)</t>
-  </si>
-  <si>
-    <t>RU r = 0.291
-RU bk = 0.004</t>
-  </si>
-  <si>
-    <t>Target_switch_lower resilience</t>
+0.48 (0.36-0.67)</t>
+  </si>
+  <si>
+    <t>14 (6-28)
+17 (12-21)</t>
+  </si>
+  <si>
+    <t>0.50 (0.01-1.00)
+0.63 (0.08-0.95)</t>
+  </si>
+  <si>
+    <t>RU r = 0.252
+RU bk = -0.024</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_lower resilience</t>
   </si>
   <si>
     <t>0.21 (0.05-0.60)
 0.07 (0.05-0.12)</t>
   </si>
   <si>
-    <t>62 (12-192)
-104 (60-156)</t>
-  </si>
-  <si>
-    <t>0.26 (0.01-0.50)
-0.29 (0.11-0.50)</t>
-  </si>
-  <si>
-    <t>RU r = 0.585
-RU bk = 0.297</t>
-  </si>
-  <si>
-    <t>Target_switch_Non-informative_r</t>
+    <t>61 (12-190)
+110 (65-164)</t>
+  </si>
+  <si>
+    <t>0.51 (0.01-1.00)
+0.34 (0.11-0.59)</t>
+  </si>
+  <si>
+    <t>RU r = 0.594
+RU bk = 0.568</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_Non-informative_r</t>
   </si>
   <si>
     <t>0.49 (0.10-1.50)
-0.14 (0.09-0.23)</t>
+0.15 (0.10-0.23)</t>
   </si>
   <si>
     <t>29 (5-98)
-49 (31-74)</t>
-  </si>
-  <si>
-    <t>0.25 (0.01-0.50)
-0.31 (0.13-0.52)</t>
-  </si>
-  <si>
-    <t>RU r = 0.630
-RU bk = 0.317</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_Euler-lotka methods</t>
-  </si>
-  <si>
-    <t>0.43 (0.20-0.80)
-0.25 (0.17-0.37)</t>
-  </si>
-  <si>
-    <t>24 (9-53)
-28 (20-38)</t>
-  </si>
-  <si>
-    <t>0.50 (0.01-1.00)
-0.38 (0.06-0.68)</t>
-  </si>
-  <si>
-    <t>RU r = 0.389
-RU bk = 0.338</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_Higher resilience</t>
+53 (32-78)</t>
+  </si>
+  <si>
+    <t>0.51 (0.01-1.00)
+0.36 (0.08-0.63)</t>
+  </si>
+  <si>
+    <t>RU r = 0.643
+RU bk = 0.450</t>
+  </si>
+  <si>
+    <t>zBRT_Euler-lotka methods</t>
+  </si>
+  <si>
+    <t>0.42 (0.20-0.80)
+0.24 (0.17-0.34)</t>
+  </si>
+  <si>
+    <t>24 (9-54)
+31 (22-41)</t>
+  </si>
+  <si>
+    <t>0.23 (0.01-0.45)
+0.24 (0.05-0.48)</t>
+  </si>
+  <si>
+    <t>RU r = 0.436
+RU bk = 0.003</t>
+  </si>
+  <si>
+    <t>zBRT_Higher resilience</t>
   </si>
   <si>
     <t>0.65 (0.40-1.00)
-0.49 (0.36-0.68)</t>
-  </si>
-  <si>
-    <t>15 (6-28)
-16 (12-21)</t>
-  </si>
-  <si>
-    <t>0.50 (0.01-1.00)
-0.67 (0.24-0.93)</t>
-  </si>
-  <si>
-    <t>RU r = 0.232
-RU bk = 0.292</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_lower resilience</t>
-  </si>
-  <si>
-    <t>62 (12-191)
-102 (61-153)</t>
-  </si>
-  <si>
-    <t>0.50 (0.01-1.00)
-0.36 (0.14-0.61)</t>
-  </si>
-  <si>
-    <t>RU r = 0.590
-RU bk = 0.609</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_Non-informative_r</t>
-  </si>
-  <si>
-    <t>29 (5-95)
-47 (30-69)</t>
-  </si>
-  <si>
-    <t>0.50 (0.01-1.00)
-0.37 (0.08-0.61)</t>
-  </si>
-  <si>
-    <t>RU r = 0.619
-RU bk = 0.422</t>
-  </si>
-  <si>
-    <t>zBRT_Euler-lotka methods</t>
-  </si>
-  <si>
-    <t>0.43 (0.20-0.80)
-0.24 (0.17-0.37)</t>
-  </si>
-  <si>
-    <t>24 (9-54)
-29 (20-38)</t>
+0.47 (0.35-0.65)</t>
+  </si>
+  <si>
+    <t>15 (7-29)
+17 (13-22)</t>
   </si>
   <si>
     <t>0.23 (0.01-0.45)
-0.25 (0.05-0.51)</t>
-  </si>
-  <si>
-    <t>RU r = 0.368
-RU bk = -0.117</t>
-  </si>
-  <si>
-    <t>zBRT_Higher resilience</t>
-  </si>
-  <si>
-    <t>0.65 (0.40-1.00)
-0.47 (0.35-0.63)</t>
-  </si>
-  <si>
-    <t>15 (6-29)
-17 (13-22)</t>
+0.22 (0.04-0.50)</t>
+  </si>
+  <si>
+    <t>RU r = 0.254
+RU bk = -0.093</t>
+  </si>
+  <si>
+    <t>zBRT_lower resilience</t>
+  </si>
+  <si>
+    <t>63 (13-197)
+113 (66-169)</t>
   </si>
   <si>
     <t>0.23 (0.01-0.45)
-0.24 (0.06-0.52)</t>
-  </si>
-  <si>
-    <t>RU r = 0.239
-RU bk = -0.095</t>
-  </si>
-  <si>
-    <t>zBRT_lower resilience</t>
-  </si>
-  <si>
-    <t>61 (13-189)
-99 (58-150)</t>
+0.28 (0.11-0.48)</t>
+  </si>
+  <si>
+    <t>RU r = 0.587
+RU bk = 0.288</t>
+  </si>
+  <si>
+    <t>zBRT_Non-informative_r</t>
+  </si>
+  <si>
+    <t>29 (5-97)
+55 (34-80)</t>
   </si>
   <si>
     <t>0.23 (0.01-0.45)
-0.29 (0.12-0.48)</t>
-  </si>
-  <si>
-    <t>RU r = 0.572
-RU bk = 0.329</t>
-  </si>
-  <si>
-    <t>zBRT_Non-informative_r</t>
-  </si>
-  <si>
-    <t>0.48 (0.10-1.50)
-0.15 (0.10-0.24)</t>
-  </si>
-  <si>
-    <t>29 (5-98)
-49 (31-72)</t>
-  </si>
-  <si>
-    <t>0.23 (0.01-0.45)
-0.27 (0.08-0.50)</t>
-  </si>
-  <si>
-    <t>RU r = 0.659
-RU bk = 0.098</t>
+0.26 (0.09-0.49)</t>
+  </si>
+  <si>
+    <t>RU r = 0.651
+RU bk = 0.154</t>
   </si>
 </sst>
 </file>
@@ -718,7 +714,7 @@
         <v>12</v>
       </c>
       <c r="G2">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -741,7 +737,7 @@
         <v>17</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -764,7 +760,7 @@
         <v>22</v>
       </c>
       <c r="G4">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -787,7 +783,7 @@
         <v>27</v>
       </c>
       <c r="G5">
-        <v>0.8999999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -798,19 +794,19 @@
         <v>28</v>
       </c>
       <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
         <v>29</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>30</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>31</v>
       </c>
-      <c r="F6" t="s">
-        <v>32</v>
-      </c>
       <c r="G6">
-        <v>19.6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -818,19 +814,19 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
         <v>33</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>34</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>35</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>36</v>
-      </c>
-      <c r="F7" t="s">
-        <v>37</v>
       </c>
       <c r="G7">
         <v>22.6</v>
@@ -841,22 +837,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
         <v>38</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>39</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>40</v>
       </c>
-      <c r="E8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" t="s">
-        <v>42</v>
-      </c>
       <c r="G8">
-        <v>24</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -864,22 +860,22 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
         <v>43</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>44</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>45</v>
       </c>
-      <c r="E9" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" t="s">
-        <v>47</v>
-      </c>
       <c r="G9">
-        <v>21.7</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -887,22 +883,22 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" t="s">
         <v>48</v>
       </c>
-      <c r="C10" t="s">
+      <c r="E10" t="s">
         <v>49</v>
       </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
         <v>50</v>
       </c>
-      <c r="E10" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" t="s">
-        <v>52</v>
-      </c>
       <c r="G10">
-        <v>62.4</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -910,22 +906,22 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" t="s">
         <v>53</v>
       </c>
-      <c r="C11" t="s">
+      <c r="E11" t="s">
         <v>54</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
         <v>55</v>
       </c>
-      <c r="E11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F11" t="s">
-        <v>57</v>
-      </c>
       <c r="G11">
-        <v>56.59999999999999</v>
+        <v>57.09999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -933,22 +929,22 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" t="s">
         <v>58</v>
       </c>
-      <c r="C12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>59</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>60</v>
       </c>
-      <c r="F12" t="s">
-        <v>61</v>
-      </c>
       <c r="G12">
-        <v>67.10000000000001</v>
+        <v>66.10000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -956,10 +952,10 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" t="s">
         <v>62</v>
-      </c>
-      <c r="C13" t="s">
-        <v>44</v>
       </c>
       <c r="D13" t="s">
         <v>63</v>
@@ -971,7 +967,7 @@
         <v>65</v>
       </c>
       <c r="G13">
-        <v>61.4</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -994,7 +990,7 @@
         <v>70</v>
       </c>
       <c r="G14">
-        <v>20</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1017,7 +1013,7 @@
         <v>75</v>
       </c>
       <c r="G15">
-        <v>21.5</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1040,7 +1036,7 @@
         <v>79</v>
       </c>
       <c r="G16">
-        <v>21.2</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1051,19 +1047,19 @@
         <v>80</v>
       </c>
       <c r="C17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" t="s">
         <v>81</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>82</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>83</v>
       </c>
-      <c r="F17" t="s">
-        <v>84</v>
-      </c>
       <c r="G17">
-        <v>21.6</v>
+        <v>22.3</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/scenarios_sumarized_macarellus_cmsy.xlsx
+++ b/Catch models/scenarios_sumarized_macarellus_cmsy.xlsx
@@ -44,288 +44,288 @@
   </si>
   <si>
     <t>0.42 (0.20-0.80)
-0.24 (0.16-0.36)</t>
-  </si>
-  <si>
-    <t>23 (9-52)
-30 (21-40)</t>
+0.24 (0.17-0.36)</t>
+  </si>
+  <si>
+    <t>24 (8-53)
+30 (21-41)</t>
   </si>
   <si>
     <t>0.14 (0.03-0.25)
 0.14 (0.05-0.26)</t>
   </si>
   <si>
-    <t>RU r = 0.359
-RU bk = 0.020</t>
+    <t>RU r = 0.377
+RU bk = 0.062</t>
   </si>
   <si>
     <t>NN_CMSY_Higher resilience</t>
   </si>
   <si>
     <t>0.65 (0.40-1.00)
-0.47 (0.35-0.62)</t>
+0.47 (0.35-0.65)</t>
+  </si>
+  <si>
+    <t>14 (6-29)
+17 (13-22)</t>
+  </si>
+  <si>
+    <t>0.14 (0.03-0.25)
+0.14 (0.05-0.27)</t>
+  </si>
+  <si>
+    <t>RU r = 0.231
+RU bk = -0.043</t>
+  </si>
+  <si>
+    <t>NN_CMSY_lower resilience</t>
+  </si>
+  <si>
+    <t>0.21 (0.05-0.60)
+0.07 (0.04-0.11)</t>
+  </si>
+  <si>
+    <t>60 (12-191)
+107 (63-163)</t>
+  </si>
+  <si>
+    <t>0.14 (0.03-0.25)
+0.17 (0.08-0.30)</t>
+  </si>
+  <si>
+    <t>RU r = 0.589
+RU bk = 0.173</t>
+  </si>
+  <si>
+    <t>NN_CMSY_Non-informative_r</t>
+  </si>
+  <si>
+    <t>0.48 (0.10-1.50)
+0.13 (0.08-0.20)</t>
+  </si>
+  <si>
+    <t>29 (5-96)
+53 (34-78)</t>
+  </si>
+  <si>
+    <t>0.14 (0.03-0.25)
+0.16 (0.06-0.27)</t>
+  </si>
+  <si>
+    <t>RU r = 0.636
+RU bk = 0.105</t>
+  </si>
+  <si>
+    <t>Target_switch_Euler-lotka methods</t>
+  </si>
+  <si>
+    <t>0.42 (0.20-0.80)
+0.24 (0.17-0.35)</t>
+  </si>
+  <si>
+    <t>24 (9-53)
+30 (21-40)</t>
+  </si>
+  <si>
+    <t>0.26 (0.01-0.50)
+0.27 (0.06-0.50)</t>
+  </si>
+  <si>
+    <t>RU r = 0.416
+RU bk = 0.000</t>
+  </si>
+  <si>
+    <t>Target_switch_Higher resilience</t>
+  </si>
+  <si>
+    <t>0.65 (0.40-1.00)
+0.46 (0.35-0.62)</t>
   </si>
   <si>
     <t>14 (6-28)
 17 (13-22)</t>
   </si>
   <si>
-    <t>0.14 (0.03-0.25)
-0.13 (0.05-0.25)</t>
-  </si>
-  <si>
-    <t>RU r = 0.291
-RU bk = -0.024</t>
-  </si>
-  <si>
-    <t>NN_CMSY_lower resilience</t>
+    <t>0.25 (0.01-0.50)
+0.24 (0.03-0.50)</t>
+  </si>
+  <si>
+    <t>RU r = 0.292
+RU bk = -0.143</t>
+  </si>
+  <si>
+    <t>Target_switch_lower resilience</t>
+  </si>
+  <si>
+    <t>63 (13-192)
+111 (67-166)</t>
+  </si>
+  <si>
+    <t>0.25 (0.01-0.50)
+0.28 (0.12-0.45)</t>
+  </si>
+  <si>
+    <t>RU r = 0.590
+RU bk = 0.369</t>
+  </si>
+  <si>
+    <t>Target_switch_Non-informative_r</t>
+  </si>
+  <si>
+    <t>0.48 (0.10-1.50)
+0.14 (0.09-0.22)</t>
+  </si>
+  <si>
+    <t>29 (5-98)
+55 (34-80)</t>
+  </si>
+  <si>
+    <t>0.26 (0.01-0.50)
+0.28 (0.09-0.48)</t>
+  </si>
+  <si>
+    <t>RU r = 0.627
+RU bk = 0.261</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_Euler-lotka methods</t>
+  </si>
+  <si>
+    <t>0.42 (0.20-0.80)
+0.25 (0.17-0.35)</t>
+  </si>
+  <si>
+    <t>24 (8-53)
+30 (22-41)</t>
+  </si>
+  <si>
+    <t>0.51 (0.01-1.00)
+0.38 (0.08-0.67)</t>
+  </si>
+  <si>
+    <t>RU r = 0.411
+RU bk = 0.405</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_Higher resilience</t>
+  </si>
+  <si>
+    <t>0.65 (0.40-1.00)
+0.48 (0.36-0.64)</t>
+  </si>
+  <si>
+    <t>14 (6-28)
+17 (13-21)</t>
+  </si>
+  <si>
+    <t>0.50 (0.01-1.00)
+0.47 (0.06-0.84)</t>
+  </si>
+  <si>
+    <t>RU r = 0.280
+RU bk = 0.127</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_lower resilience</t>
   </si>
   <si>
     <t>0.21 (0.05-0.60)
-0.07 (0.04-0.11)</t>
-  </si>
-  <si>
-    <t>61 (12-197)
-112 (65-169)</t>
-  </si>
-  <si>
-    <t>0.14 (0.03-0.25)
-0.17 (0.07-0.30)</t>
-  </si>
-  <si>
-    <t>RU r = 0.590
-RU bk = 0.110</t>
-  </si>
-  <si>
-    <t>NN_CMSY_Non-informative_r</t>
+0.07 (0.05-0.11)</t>
+  </si>
+  <si>
+    <t>65 (12-201)
+118 (71-175)</t>
+  </si>
+  <si>
+    <t>0.51 (0.01-1.00)
+0.32 (0.11-0.59)</t>
+  </si>
+  <si>
+    <t>RU r = 0.626
+RU bk = 0.578</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_Non-informative_r</t>
+  </si>
+  <si>
+    <t>0.49 (0.10-1.50)
+0.14 (0.09-0.22)</t>
+  </si>
+  <si>
+    <t>29 (5-97)
+54 (33-79)</t>
+  </si>
+  <si>
+    <t>0.50 (0.01-1.00)
+0.33 (0.10-0.59)</t>
+  </si>
+  <si>
+    <t>RU r = 0.636
+RU bk = 0.547</t>
+  </si>
+  <si>
+    <t>zBRT_Euler-lotka methods</t>
+  </si>
+  <si>
+    <t>24 (9-53)
+30 (20-40)</t>
+  </si>
+  <si>
+    <t>0.22 (0.01-0.44)
+0.21 (0.06-0.41)</t>
+  </si>
+  <si>
+    <t>RU r = 0.391
+RU bk = 0.121</t>
+  </si>
+  <si>
+    <t>zBRT_Higher resilience</t>
+  </si>
+  <si>
+    <t>15 (6-29)
+17 (12-21)</t>
+  </si>
+  <si>
+    <t>0.23 (0.01-0.44)
+0.21 (0.05-0.50)</t>
+  </si>
+  <si>
+    <t>RU r = 0.275
+RU bk = -0.089</t>
+  </si>
+  <si>
+    <t>zBRT_lower resilience</t>
+  </si>
+  <si>
+    <t>61 (13-189)
+108 (63-163)</t>
+  </si>
+  <si>
+    <t>0.22 (0.01-0.44)
+0.26 (0.10-0.45)</t>
+  </si>
+  <si>
+    <t>RU r = 0.571
+RU bk = 0.302</t>
+  </si>
+  <si>
+    <t>zBRT_Non-informative_r</t>
   </si>
   <si>
     <t>0.49 (0.10-1.50)
 0.13 (0.08-0.20)</t>
   </si>
   <si>
-    <t>29 (5-96)
-53 (35-78)</t>
-  </si>
-  <si>
-    <t>0.14 (0.03-0.25)
-0.14 (0.05-0.25)</t>
-  </si>
-  <si>
-    <t>RU r = 0.632
-RU bk = 0.119</t>
-  </si>
-  <si>
-    <t>Target_switch_Euler-lotka methods</t>
-  </si>
-  <si>
-    <t>24 (9-53)
-31 (21-41)</t>
-  </si>
-  <si>
-    <t>0.26 (0.01-0.50)
-0.26 (0.05-0.55)</t>
-  </si>
-  <si>
-    <t>RU r = 0.393
-RU bk = -0.096</t>
-  </si>
-  <si>
-    <t>Target_switch_Higher resilience</t>
-  </si>
-  <si>
-    <t>0.65 (0.40-1.00)
-0.46 (0.34-0.64)</t>
-  </si>
-  <si>
-    <t>14 (6-29)
-17 (12-22)</t>
-  </si>
-  <si>
-    <t>0.25 (0.01-0.50)
-0.29 (0.05-0.63)</t>
-  </si>
-  <si>
-    <t>RU r = 0.216
-RU bk = -0.125</t>
-  </si>
-  <si>
-    <t>Target_switch_lower resilience</t>
-  </si>
-  <si>
-    <t>61 (12-192)
-110 (65-169)</t>
-  </si>
-  <si>
-    <t>0.25 (0.01-0.50)
-0.30 (0.10-0.47)</t>
-  </si>
-  <si>
-    <t>RU r = 0.593
-RU bk = 0.305</t>
-  </si>
-  <si>
-    <t>Target_switch_Non-informative_r</t>
-  </si>
-  <si>
-    <t>0.49 (0.10-1.50)
-0.14 (0.09-0.21)</t>
-  </si>
-  <si>
-    <t>29 (5-99)
-55 (35-81)</t>
-  </si>
-  <si>
-    <t>0.26 (0.01-0.50)
-0.30 (0.08-0.51)</t>
-  </si>
-  <si>
-    <t>RU r = 0.647
-RU bk = 0.107</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_Euler-lotka methods</t>
-  </si>
-  <si>
-    <t>0.42 (0.20-0.80)
-0.25 (0.17-0.37)</t>
-  </si>
-  <si>
-    <t>24 (8-54)
-30 (21-41)</t>
-  </si>
-  <si>
-    <t>0.51 (0.01-1.00)
-0.41 (0.06-0.82)</t>
-  </si>
-  <si>
-    <t>RU r = 0.404
+    <t>29 (5-97)
+55 (35-79)</t>
+  </si>
+  <si>
+    <t>0.23 (0.01-0.44)
+0.24 (0.10-0.42)</t>
+  </si>
+  <si>
+    <t>RU r = 0.623
 RU bk = 0.297</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_Higher resilience</t>
-  </si>
-  <si>
-    <t>0.65 (0.40-1.00)
-0.48 (0.36-0.67)</t>
-  </si>
-  <si>
-    <t>14 (6-28)
-17 (12-21)</t>
-  </si>
-  <si>
-    <t>0.50 (0.01-1.00)
-0.63 (0.08-0.95)</t>
-  </si>
-  <si>
-    <t>RU r = 0.252
-RU bk = -0.024</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_lower resilience</t>
-  </si>
-  <si>
-    <t>0.21 (0.05-0.60)
-0.07 (0.05-0.12)</t>
-  </si>
-  <si>
-    <t>61 (12-190)
-110 (65-164)</t>
-  </si>
-  <si>
-    <t>0.51 (0.01-1.00)
-0.34 (0.11-0.59)</t>
-  </si>
-  <si>
-    <t>RU r = 0.594
-RU bk = 0.568</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_Non-informative_r</t>
-  </si>
-  <si>
-    <t>0.49 (0.10-1.50)
-0.15 (0.10-0.23)</t>
-  </si>
-  <si>
-    <t>29 (5-98)
-53 (32-78)</t>
-  </si>
-  <si>
-    <t>0.51 (0.01-1.00)
-0.36 (0.08-0.63)</t>
-  </si>
-  <si>
-    <t>RU r = 0.643
-RU bk = 0.450</t>
-  </si>
-  <si>
-    <t>zBRT_Euler-lotka methods</t>
-  </si>
-  <si>
-    <t>0.42 (0.20-0.80)
-0.24 (0.17-0.34)</t>
-  </si>
-  <si>
-    <t>24 (9-54)
-31 (22-41)</t>
-  </si>
-  <si>
-    <t>0.23 (0.01-0.45)
-0.24 (0.05-0.48)</t>
-  </si>
-  <si>
-    <t>RU r = 0.436
-RU bk = 0.003</t>
-  </si>
-  <si>
-    <t>zBRT_Higher resilience</t>
-  </si>
-  <si>
-    <t>0.65 (0.40-1.00)
-0.47 (0.35-0.65)</t>
-  </si>
-  <si>
-    <t>15 (7-29)
-17 (13-22)</t>
-  </si>
-  <si>
-    <t>0.23 (0.01-0.45)
-0.22 (0.04-0.50)</t>
-  </si>
-  <si>
-    <t>RU r = 0.254
-RU bk = -0.093</t>
-  </si>
-  <si>
-    <t>zBRT_lower resilience</t>
-  </si>
-  <si>
-    <t>63 (13-197)
-113 (66-169)</t>
-  </si>
-  <si>
-    <t>0.23 (0.01-0.45)
-0.28 (0.11-0.48)</t>
-  </si>
-  <si>
-    <t>RU r = 0.587
-RU bk = 0.288</t>
-  </si>
-  <si>
-    <t>zBRT_Non-informative_r</t>
-  </si>
-  <si>
-    <t>29 (5-97)
-55 (34-80)</t>
-  </si>
-  <si>
-    <t>0.23 (0.01-0.45)
-0.26 (0.09-0.49)</t>
-  </si>
-  <si>
-    <t>RU r = 0.651
-RU bk = 0.154</t>
   </si>
 </sst>
 </file>
@@ -714,7 +714,7 @@
         <v>12</v>
       </c>
       <c r="G2">
-        <v>0.4</v>
+        <v>0.7000000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -737,7 +737,7 @@
         <v>17</v>
       </c>
       <c r="G3">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -760,7 +760,7 @@
         <v>22</v>
       </c>
       <c r="G4">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -783,7 +783,7 @@
         <v>27</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -794,19 +794,19 @@
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G6">
-        <v>21</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -814,22 +814,22 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G7">
-        <v>22.6</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -837,22 +837,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
         <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G8">
-        <v>25.8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -860,22 +860,22 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G9">
-        <v>23.3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -883,22 +883,22 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G10">
-        <v>60.8</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -906,19 +906,19 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G11">
         <v>57.09999999999999</v>
@@ -929,22 +929,22 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G12">
-        <v>66.10000000000001</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -952,22 +952,22 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G13">
-        <v>58.4</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -975,10 +975,10 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="D14" t="s">
         <v>68</v>
@@ -990,7 +990,7 @@
         <v>70</v>
       </c>
       <c r="G14">
-        <v>19.9</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1001,19 +1001,19 @@
         <v>71</v>
       </c>
       <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
         <v>72</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>73</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>74</v>
       </c>
-      <c r="F15" t="s">
-        <v>75</v>
-      </c>
       <c r="G15">
-        <v>22.9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1021,22 +1021,22 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
       </c>
       <c r="D16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" t="s">
         <v>77</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>78</v>
       </c>
-      <c r="F16" t="s">
-        <v>79</v>
-      </c>
       <c r="G16">
-        <v>21.9</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1044,10 +1044,10 @@
         <v>7</v>
       </c>
       <c r="B17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" t="s">
         <v>80</v>
-      </c>
-      <c r="C17" t="s">
-        <v>42</v>
       </c>
       <c r="D17" t="s">
         <v>81</v>
@@ -1059,7 +1059,7 @@
         <v>83</v>
       </c>
       <c r="G17">
-        <v>22.3</v>
+        <v>23.2</v>
       </c>
     </row>
   </sheetData>
